--- a/docx/Libro1.xlsx
+++ b/docx/Libro1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tesis\docx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{337E2C63-D2A2-4CD5-954F-A56E431C6E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39CD1B6-6C5A-46D5-929B-987CE205F3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{78943573-3778-4549-A331-0ED2CCDFF9BA}"/>
   </bookViews>
@@ -480,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5195291-9847-4788-9AAD-1BAFD2176028}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -543,7 +543,7 @@
         <v>1024</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G27" si="2">F3/D3</f>
+        <f t="shared" ref="G3:G26" si="2">F3/D3</f>
         <v>1.0158730158730158</v>
       </c>
     </row>
@@ -885,7 +885,7 @@
         <v>0.6696428571428571</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -911,7 +911,7 @@
         <v>6.7347560975609753</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -937,7 +937,7 @@
         <v>6.328125</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -963,7 +963,7 @@
         <v>0.14117647058823529</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -989,7 +989,7 @@
         <v>1.639344262295082</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>4.7850467289719623</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>1.8957345971563982E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>2.4820512820512821</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>0.47647058823529409</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>0.30625000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>1.9395973154362416</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C27">
         <f>SUM(C2:C26)</f>
         <v>10298</v>
@@ -1165,6 +1165,11 @@
       <c r="G27">
         <f t="shared" si="3"/>
         <v>152.01448881615724</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H30">
+        <v>75.689300000000003</v>
       </c>
     </row>
   </sheetData>
